--- a/output/pdf_financials_xlsx/BTE.xlsx
+++ b/output/pdf_financials_xlsx/BTE.xlsx
@@ -2320,28 +2320,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>10.177</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.847</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.837</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>18.368</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.142</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.705</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
@@ -2350,19 +2350,19 @@
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5.572</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>55.815</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>55.815</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>16.61</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>953.1130000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2424,28 +2424,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>10.177</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.847</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.837</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>18.368</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.142</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.705</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0</v>
@@ -2454,19 +2454,19 @@
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>5.572</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>55.815</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>55.815</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>16.61</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>953.1130000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3048,28 +3048,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>42.385</v>
+        <v>32.208</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>21.203</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>19.624</v>
+        <v>11.777</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>23.367</v>
+        <v>21.53</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>103.596</v>
+        <v>85.22799999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>221.55</v>
+        <v>220.408</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>106.82</v>
+        <v>106.573</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.924</v>
+        <v>2.219</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>18.51</v>
@@ -3078,19 +3078,19 @@
         <v>79.58199999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>11.005</v>
+        <v>5.433</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>100.619</v>
+        <v>44.804</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>100.619</v>
+        <v>44.804</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>62.361</v>
+        <v>45.751</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1055.136</v>
+        <v>102.023</v>
       </c>
     </row>
     <row r="49">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">

--- a/output/pdf_financials_xlsx/BTE.xlsx
+++ b/output/pdf_financials_xlsx/BTE.xlsx
@@ -6822,13 +6822,13 @@
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>1401.317</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>606.095</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>109.939</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
@@ -40690,7 +40690,11 @@
           <t>Issuance of common shares, net of issuance costs (note 12)</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -42383,7 +42387,11 @@
           <t>Issuance of common shares, net of issuance costs (note 14)</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -44440,7 +44448,11 @@
           <t>Issuance of common shares, net of issuance costs (note 15)</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BTE.xlsx
+++ b/output/pdf_financials_xlsx/BTE.xlsx
@@ -1316,7 +1316,7 @@
         <v>-52.141</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-107.598</v>
+        <v>-10.162</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>6.821</v>
@@ -1328,10 +1328,10 @@
         <v>-8.907</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>8.042</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>156.428</v>
+        <v>1.085</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0.035</v>
@@ -1543,10 +1543,8 @@
       <c r="H20" s="3" t="n">
         <v>-1495.933</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="3" t="n">
+        <v>-749.745</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>87.17400000000001</v>
@@ -1564,10 +1562,10 @@
         <v>-233.356</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>236.597</v>
+        <v>-97.453</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-603.779</v>
+        <v>-276.845</v>
       </c>
     </row>
     <row r="21">
@@ -1702,7 +1700,7 @@
         <v>-1495.933</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-757.787</v>
+        <v>-749.745</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>87.17400000000001</v>
@@ -2192,7 +2190,7 @@
         <v>19.34207060796148</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>28.58676217019005</v>
+        <v>2.699852015590171</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>3.133973819992924</v>
@@ -2204,10 +2202,10 @@
         <v>-0.5989807844651002</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.061248081584931</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-225.8757616888555</v>
+        <v>-1.566696508504924</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0.008195262669876087</v>
@@ -4260,19 +4258,19 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>5.798</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>13.391</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>13.391</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>9.193</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>7.175</v>
       </c>
     </row>
     <row r="71">
@@ -4312,19 +4310,19 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>5.798</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>13.391</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>13.391</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>9.193</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>7.175</v>
       </c>
     </row>
     <row r="72">
@@ -4520,19 +4518,19 @@
         <v>1.986</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>26.045</v>
+        <v>20.247</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>80.72799999999999</v>
+        <v>67.337</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>80.72799999999999</v>
+        <v>67.337</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>61.253</v>
+        <v>52.06</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>93.80500000000001</v>
+        <v>86.63</v>
       </c>
     </row>
     <row r="76">
@@ -4676,19 +4674,19 @@
         <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>16.056</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>16.056</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>15.459</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>15.844</v>
       </c>
     </row>
     <row r="79">
@@ -4728,19 +4726,19 @@
         <v>0</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>848.749</v>
+        <v>864.8049999999999</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>848.749</v>
+        <v>864.8049999999999</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>324.346</v>
+        <v>339.805</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>1.138</v>
+        <v>16.982</v>
       </c>
     </row>
     <row r="80">
@@ -4787,22 +4785,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.004710558362165697</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.2218901164862394</v>
+        <v>0.2295885034771758</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.2218901164862394</v>
+        <v>0.2295885034771758</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.07776198091109827</v>
+        <v>0.08367229999448575</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.0004763401671543782</v>
+        <v>0.01011155484881223</v>
       </c>
     </row>
     <row r="81">
@@ -5050,19 +5046,19 @@
         <v>3321.774</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>2966.874</v>
+        <v>2958.789</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>2787.095</v>
+        <v>2771.039</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>2787.095</v>
+        <v>2771.039</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>3264.389</v>
+        <v>3248.93</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>955.227</v>
+        <v>939.383</v>
       </c>
     </row>
     <row r="86">
@@ -5736,7 +5732,7 @@
         <v>-1495.933</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-757.787</v>
+        <v>-749.745</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>87.17400000000001</v>
@@ -6892,16 +6888,16 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-158.977</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-221.932</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-222.2</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-29.42</v>
       </c>
     </row>
     <row r="122">
@@ -9480,7 +9476,11 @@
           <t>Lease obligations 8</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10174,7 +10174,11 @@
           <t>Lease obligations 8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -11967,7 +11971,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -12497,7 +12505,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14704,7 +14716,11 @@
           <t>Lease obligations 9</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -15246,7 +15262,11 @@
           <t>Lease obligations 9</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -30448,7 +30468,11 @@
           <t>Deferred income tax expense 16</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -31251,7 +31275,11 @@
           <t>Repurchase of common shares 12</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -32783,7 +32811,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -33584,7 +33616,11 @@
           <t>Deferred income tax expense (recovery) 15</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -34387,7 +34423,11 @@
           <t>Repurchase of common shares 11</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -36632,7 +36672,11 @@
           <t>Deferred income tax recovery 17</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -38475,7 +38519,11 @@
           <t>Deferred income tax recovery (note 16)</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -40156,7 +40204,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -43639,7 +43691,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -46606,7 +46662,11 @@
           <t>Deferred income tax expense (note 16)</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -47686,7 +47746,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E449" s="5" t="n">
         <v>-30.457</v>
       </c>
@@ -51318,7 +51382,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
           <t>-</t>
@@ -54961,7 +55029,11 @@
           <t>Deferred income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -56225,7 +56297,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -57730,7 +57806,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E563" t="inlineStr">
         <is>
           <t>-</t>
@@ -57819,7 +57899,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -59114,7 +59198,11 @@
           <t>Current income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
           <t>-</t>
@@ -59203,7 +59291,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
@@ -59292,7 +59384,11 @@
           <t>Income tax (recovery) expense total</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E581" s="5" t="n">
         <v>-19.087</v>
       </c>
@@ -60281,7 +60377,11 @@
           <t>Deferred income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -62684,7 +62784,11 @@
           <t>Current income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
           <t>-</t>
